--- a/template/FI운용본부수탁고_양식.xlsx
+++ b/template/FI운용본부수탁고_양식.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Cowork\2026-07-23_수탁고-자동화\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D8456-0140-40AD-B9B2-D9297A2490B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C44E2E-8786-4784-869F-28AFD98CF75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B10785B8-A63F-44BF-85F7-F1F5C32EAF21}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{B10785B8-A63F-44BF-85F7-F1F5C32EAF21}"/>
   </bookViews>
   <sheets>
     <sheet name="월말기준수탁고" sheetId="1" r:id="rId1"/>
@@ -1273,7 +1273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1760,15 +1760,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1899,6 +1890,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3665,20 +3662,20 @@
       <c r="M1" s="6"/>
     </row>
     <row r="2" spans="1:48" s="10" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="201"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="198"/>
       <c r="N2" s="7"/>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -3728,10 +3725,10 @@
       <c r="J3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="202">
+      <c r="L3" s="199">
         <v>46224</v>
       </c>
-      <c r="M3" s="203"/>
+      <c r="M3" s="200"/>
       <c r="N3" s="15"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
@@ -3882,7 +3879,7 @@
     </row>
     <row r="7" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28"/>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="165" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="35">
@@ -3954,7 +3951,7 @@
     </row>
     <row r="8" spans="1:48" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28"/>
-      <c r="B8" s="169" t="s">
+      <c r="B8" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="35">
@@ -4026,7 +4023,7 @@
     </row>
     <row r="9" spans="1:48" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28"/>
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="166" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="35">
@@ -4094,7 +4091,7 @@
     </row>
     <row r="10" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="28"/>
-      <c r="B10" s="169" t="s">
+      <c r="B10" s="166" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="35">
@@ -4162,7 +4159,7 @@
     </row>
     <row r="11" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28"/>
-      <c r="B11" s="170" t="s">
+      <c r="B11" s="167" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="47">
@@ -4234,7 +4231,7 @@
     </row>
     <row r="12" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20"/>
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="168" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="35">
@@ -4280,7 +4277,7 @@
     </row>
     <row r="13" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
-      <c r="B13" s="169" t="s">
+      <c r="B13" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="37">
@@ -4326,7 +4323,7 @@
     </row>
     <row r="14" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
-      <c r="B14" s="169" t="s">
+      <c r="B14" s="166" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="37">
@@ -4368,7 +4365,7 @@
     </row>
     <row r="15" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
-      <c r="B15" s="170" t="s">
+      <c r="B15" s="167" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="47"/>
@@ -4413,7 +4410,7 @@
     </row>
     <row r="16" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
-      <c r="B16" s="168" t="s">
+      <c r="B16" s="165" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="35">
@@ -4454,7 +4451,7 @@
     </row>
     <row r="17" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
-      <c r="B17" s="169" t="s">
+      <c r="B17" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="37">
@@ -4495,7 +4492,7 @@
     </row>
     <row r="18" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
-      <c r="B18" s="169" t="s">
+      <c r="B18" s="166" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="37">
@@ -4532,7 +4529,7 @@
     </row>
     <row r="19" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
-      <c r="B19" s="169" t="s">
+      <c r="B19" s="166" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="37">
@@ -4569,7 +4566,7 @@
     </row>
     <row r="20" spans="1:48" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20"/>
-      <c r="B20" s="170" t="s">
+      <c r="B20" s="167" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="47">
@@ -4610,31 +4607,31 @@
     </row>
     <row r="21" spans="1:48" ht="23.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
-      <c r="B21" s="172" t="s">
+      <c r="B21" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="173">
+      <c r="C21" s="170">
         <v>269315.74075638998</v>
       </c>
-      <c r="D21" s="174">
+      <c r="D21" s="171">
         <v>349940.90917380003</v>
       </c>
-      <c r="E21" s="173">
+      <c r="E21" s="170">
         <v>361698.06721423002</v>
       </c>
-      <c r="F21" s="173">
+      <c r="F21" s="170">
         <v>361698.06721423002</v>
       </c>
-      <c r="G21" s="174">
+      <c r="G21" s="171">
         <v>373827.37736832001</v>
       </c>
-      <c r="H21" s="173">
+      <c r="H21" s="170">
         <v>399927.38394253998</v>
       </c>
-      <c r="I21" s="175">
+      <c r="I21" s="172">
         <v>68000</v>
       </c>
-      <c r="J21" s="176">
+      <c r="J21" s="173">
         <v>0.35127159109588207</v>
       </c>
       <c r="K21" s="57">
@@ -4653,7 +4650,7 @@
     </row>
     <row r="22" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="61"/>
-      <c r="B22" s="169" t="s">
+      <c r="B22" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="62">
@@ -4699,7 +4696,7 @@
     </row>
     <row r="23" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="69"/>
-      <c r="B23" s="169" t="s">
+      <c r="B23" s="166" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="62">
@@ -4749,7 +4746,7 @@
     </row>
     <row r="24" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="69"/>
-      <c r="B24" s="169" t="s">
+      <c r="B24" s="166" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="62">
@@ -4799,7 +4796,7 @@
     </row>
     <row r="25" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="69"/>
-      <c r="B25" s="170" t="s">
+      <c r="B25" s="167" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="73">
@@ -4912,28 +4909,28 @@
     </row>
     <row r="28" spans="1:48" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="69"/>
-      <c r="B28" s="204" t="s">
+      <c r="B28" s="201" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="206" t="s">
+      <c r="C28" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="207"/>
-      <c r="E28" s="208"/>
-      <c r="F28" s="206" t="s">
+      <c r="D28" s="204"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="207"/>
-      <c r="H28" s="208"/>
-      <c r="I28" s="206" t="s">
+      <c r="G28" s="204"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="J28" s="207"/>
-      <c r="K28" s="208"/>
-      <c r="L28" s="209" t="s">
+      <c r="J28" s="204"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="206" t="s">
         <v>31</v>
       </c>
-      <c r="M28" s="209" t="s">
+      <c r="M28" s="206" t="s">
         <v>32</v>
       </c>
       <c r="R28" s="11"/>
@@ -4953,7 +4950,7 @@
     </row>
     <row r="29" spans="1:48" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="69"/>
-      <c r="B29" s="205"/>
+      <c r="B29" s="202"/>
       <c r="C29" s="90">
         <v>46022</v>
       </c>
@@ -4981,8 +4978,8 @@
       <c r="K29" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="210"/>
-      <c r="M29" s="210"/>
+      <c r="L29" s="207"/>
+      <c r="M29" s="207"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
       <c r="AG29" s="8"/>
@@ -5000,7 +4997,7 @@
     </row>
     <row r="30" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="93"/>
-      <c r="B30" s="177" t="s">
+      <c r="B30" s="174" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="35">
@@ -5053,7 +5050,7 @@
     </row>
     <row r="31" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="93"/>
-      <c r="B31" s="178" t="s">
+      <c r="B31" s="175" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="35">
@@ -5106,7 +5103,7 @@
     </row>
     <row r="32" spans="1:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="93"/>
-      <c r="B32" s="178" t="s">
+      <c r="B32" s="175" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="35">
@@ -5150,7 +5147,7 @@
     </row>
     <row r="33" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="97"/>
-      <c r="B33" s="178" t="s">
+      <c r="B33" s="175" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="35">
@@ -5206,7 +5203,7 @@
     </row>
     <row r="34" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
-      <c r="B34" s="178" t="s">
+      <c r="B34" s="175" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="35">
@@ -5269,7 +5266,7 @@
     </row>
     <row r="35" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
-      <c r="B35" s="178" t="s">
+      <c r="B35" s="175" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="37">
@@ -5322,7 +5319,7 @@
     </row>
     <row r="36" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="178" t="s">
+      <c r="B36" s="175" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="37">
@@ -5381,7 +5378,7 @@
     </row>
     <row r="37" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="178" t="s">
+      <c r="B37" s="175" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="37">
@@ -5436,7 +5433,7 @@
     </row>
     <row r="38" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="178" t="s">
+      <c r="B38" s="175" t="s">
         <v>118</v>
       </c>
       <c r="C38" s="37"/>
@@ -5487,7 +5484,7 @@
     </row>
     <row r="39" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="178" t="s">
+      <c r="B39" s="175" t="s">
         <v>119</v>
       </c>
       <c r="C39" s="37"/>
@@ -5538,40 +5535,40 @@
     </row>
     <row r="40" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="179" t="s">
+      <c r="B40" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="173">
+      <c r="C40" s="170">
         <v>113994.94309587999</v>
       </c>
-      <c r="D40" s="173">
+      <c r="D40" s="170">
         <v>142381.77506461</v>
       </c>
-      <c r="E40" s="174">
+      <c r="E40" s="171">
         <v>28386.831968729999</v>
       </c>
-      <c r="F40" s="173">
+      <c r="F40" s="170">
         <v>163742.43703909</v>
       </c>
-      <c r="G40" s="173">
+      <c r="G40" s="170">
         <v>150533.68376956999</v>
       </c>
-      <c r="H40" s="174">
+      <c r="H40" s="171">
         <v>-13208.75326951995</v>
       </c>
-      <c r="I40" s="173">
+      <c r="I40" s="170">
         <v>72203.529038829991</v>
       </c>
-      <c r="J40" s="173">
+      <c r="J40" s="170">
         <v>80911.918534140015</v>
       </c>
-      <c r="K40" s="174">
+      <c r="K40" s="171">
         <v>8708.3894953100244</v>
       </c>
-      <c r="L40" s="180">
+      <c r="L40" s="177">
         <v>23886.468194520068</v>
       </c>
-      <c r="M40" s="180">
+      <c r="M40" s="177">
         <v>373827.37736832001</v>
       </c>
       <c r="N40" s="99"/>
@@ -5641,19 +5638,19 @@
     </row>
     <row r="43" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="193" t="s">
+      <c r="B43" s="190" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="194"/>
+      <c r="C43" s="191"/>
       <c r="D43" s="106" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="106"/>
       <c r="F43" s="107"/>
-      <c r="G43" s="197" t="s">
+      <c r="G43" s="194" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="194"/>
+      <c r="H43" s="191"/>
       <c r="I43" s="106" t="s">
         <v>44</v>
       </c>
@@ -5674,8 +5671,8 @@
     </row>
     <row r="44" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="195"/>
-      <c r="C44" s="196"/>
+      <c r="B44" s="192"/>
+      <c r="C44" s="193"/>
       <c r="D44" s="91">
         <v>46022</v>
       </c>
@@ -5685,8 +5682,8 @@
       <c r="F44" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="198"/>
-      <c r="H44" s="196"/>
+      <c r="G44" s="195"/>
+      <c r="H44" s="193"/>
       <c r="I44" s="91">
         <v>46022</v>
       </c>
@@ -5716,10 +5713,10 @@
     </row>
     <row r="45" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="181" t="s">
+      <c r="B45" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="182"/>
+      <c r="C45" s="179"/>
       <c r="D45" s="111">
         <v>26151.576618660001</v>
       </c>
@@ -5729,10 +5726,10 @@
       <c r="F45" s="94">
         <v>24199.900181590001</v>
       </c>
-      <c r="G45" s="189" t="s">
+      <c r="G45" s="186" t="s">
         <v>49</v>
       </c>
-      <c r="H45" s="182"/>
+      <c r="H45" s="179"/>
       <c r="I45" s="111">
         <v>1717.6486722</v>
       </c>
@@ -5762,10 +5759,10 @@
     </row>
     <row r="46" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="183" t="s">
+      <c r="B46" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="184"/>
+      <c r="C46" s="181"/>
       <c r="D46" s="116">
         <v>13347.724352560001</v>
       </c>
@@ -5775,10 +5772,10 @@
       <c r="F46" s="96">
         <v>2440.4911385599989</v>
       </c>
-      <c r="G46" s="190" t="s">
+      <c r="G46" s="187" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="184"/>
+      <c r="H46" s="181"/>
       <c r="I46" s="116">
         <v>1220.5848338599999</v>
       </c>
@@ -5806,10 +5803,10 @@
     </row>
     <row r="47" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="183" t="s">
+      <c r="B47" s="180" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="184"/>
+      <c r="C47" s="181"/>
       <c r="D47" s="116">
         <v>8107.1352466600001</v>
       </c>
@@ -5819,10 +5816,10 @@
       <c r="F47" s="96">
         <v>2360.5023480499999</v>
       </c>
-      <c r="G47" s="190" t="s">
+      <c r="G47" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="184"/>
+      <c r="H47" s="181"/>
       <c r="I47" s="116">
         <v>1179.30829002</v>
       </c>
@@ -5850,10 +5847,10 @@
     </row>
     <row r="48" spans="1:45" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="183" t="s">
+      <c r="B48" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="184"/>
+      <c r="C48" s="181"/>
       <c r="D48" s="116">
         <v>9922.8437902700007</v>
       </c>
@@ -5863,10 +5860,10 @@
       <c r="F48" s="96">
         <v>2165.182011209999</v>
       </c>
-      <c r="G48" s="190" t="s">
+      <c r="G48" s="187" t="s">
         <v>56</v>
       </c>
-      <c r="H48" s="184"/>
+      <c r="H48" s="181"/>
       <c r="I48" s="116">
         <v>1023.6289821</v>
       </c>
@@ -5893,10 +5890,10 @@
       <c r="AF48" s="9"/>
     </row>
     <row r="49" spans="2:48" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="185" t="s">
+      <c r="B49" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="186"/>
+      <c r="C49" s="183"/>
       <c r="D49" s="119">
         <v>4651.0387039300003</v>
       </c>
@@ -5906,10 +5903,10 @@
       <c r="F49" s="121">
         <v>1891.088451529999</v>
       </c>
-      <c r="G49" s="191" t="s">
+      <c r="G49" s="188" t="s">
         <v>58</v>
       </c>
-      <c r="H49" s="186"/>
+      <c r="H49" s="183"/>
       <c r="I49" s="119">
         <v>3386.53014609</v>
       </c>
@@ -5941,10 +5938,10 @@
       <c r="AV49" s="2"/>
     </row>
     <row r="50" spans="2:48" ht="23.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="183" t="s">
+      <c r="B50" s="180" t="s">
         <v>59</v>
       </c>
-      <c r="C50" s="184"/>
+      <c r="C50" s="181"/>
       <c r="D50" s="124"/>
       <c r="E50" s="37">
         <v>2002.63267774</v>
@@ -5952,10 +5949,10 @@
       <c r="F50" s="125">
         <v>2002.63267774</v>
       </c>
-      <c r="G50" s="190" t="s">
+      <c r="G50" s="187" t="s">
         <v>60</v>
       </c>
-      <c r="H50" s="184"/>
+      <c r="H50" s="181"/>
       <c r="I50" s="124">
         <v>28095.517445670001</v>
       </c>
@@ -5988,10 +5985,10 @@
       <c r="AV50" s="2"/>
     </row>
     <row r="51" spans="2:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="183" t="s">
+      <c r="B51" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="184"/>
+      <c r="C51" s="181"/>
       <c r="D51" s="124"/>
       <c r="E51" s="37">
         <v>1781.3013215799999</v>
@@ -5999,10 +5996,10 @@
       <c r="F51" s="125">
         <v>1781.3013215799999</v>
       </c>
-      <c r="G51" s="190" t="s">
+      <c r="G51" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="H51" s="184"/>
+      <c r="H51" s="181"/>
       <c r="I51" s="124">
         <v>2004.8326924600001</v>
       </c>
@@ -6031,10 +6028,10 @@
       <c r="AV51" s="2"/>
     </row>
     <row r="52" spans="2:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="183" t="s">
+      <c r="B52" s="180" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="184"/>
+      <c r="C52" s="181"/>
       <c r="D52" s="124">
         <v>4596.7196875</v>
       </c>
@@ -6044,10 +6041,10 @@
       <c r="F52" s="125">
         <v>1702.5910197400001</v>
       </c>
-      <c r="G52" s="190" t="s">
+      <c r="G52" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="H52" s="184"/>
+      <c r="H52" s="181"/>
       <c r="I52" s="124">
         <v>1587.3971509400001</v>
       </c>
@@ -6076,10 +6073,10 @@
       <c r="AV52" s="2"/>
     </row>
     <row r="53" spans="2:48" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="183" t="s">
+      <c r="B53" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="184"/>
+      <c r="C53" s="181"/>
       <c r="D53" s="124">
         <v>2320.46071725</v>
       </c>
@@ -6089,10 +6086,10 @@
       <c r="F53" s="125">
         <v>1233.00805988</v>
       </c>
-      <c r="G53" s="190" t="s">
+      <c r="G53" s="187" t="s">
         <v>66</v>
       </c>
-      <c r="H53" s="184"/>
+      <c r="H53" s="181"/>
       <c r="I53" s="124">
         <v>1040</v>
       </c>
@@ -6122,10 +6119,10 @@
       <c r="AV53" s="2"/>
     </row>
     <row r="54" spans="2:48" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="185" t="s">
+      <c r="B54" s="182" t="s">
         <v>67</v>
       </c>
-      <c r="C54" s="186"/>
+      <c r="C54" s="183"/>
       <c r="D54" s="129"/>
       <c r="E54" s="130">
         <v>1219.11133877</v>
@@ -6133,10 +6130,10 @@
       <c r="F54" s="131">
         <v>1219.11133877</v>
       </c>
-      <c r="G54" s="191" t="s">
+      <c r="G54" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="H54" s="186"/>
+      <c r="H54" s="183"/>
       <c r="I54" s="129">
         <v>1000</v>
       </c>
@@ -6163,10 +6160,10 @@
       <c r="AV54" s="2"/>
     </row>
     <row r="55" spans="2:48" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="183" t="s">
+      <c r="B55" s="180" t="s">
         <v>69</v>
       </c>
-      <c r="C55" s="184"/>
+      <c r="C55" s="181"/>
       <c r="D55" s="124">
         <v>7318.50441649</v>
       </c>
@@ -6176,10 +6173,10 @@
       <c r="F55" s="125">
         <v>5004.8200050799996</v>
       </c>
-      <c r="G55" s="190" t="s">
+      <c r="G55" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="H55" s="184"/>
+      <c r="H55" s="181"/>
       <c r="I55" s="124">
         <v>21997.360726769999</v>
       </c>
@@ -6205,10 +6202,10 @@
       <c r="AV55" s="2"/>
     </row>
     <row r="56" spans="2:48" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="183" t="s">
+      <c r="B56" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="184"/>
+      <c r="C56" s="181"/>
       <c r="D56" s="124">
         <v>5083.9695914900003</v>
       </c>
@@ -6218,10 +6215,10 @@
       <c r="F56" s="125">
         <v>4266.5744771600002</v>
       </c>
-      <c r="G56" s="190" t="s">
+      <c r="G56" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="H56" s="184"/>
+      <c r="H56" s="181"/>
       <c r="I56" s="124">
         <v>4740.8503354799996</v>
       </c>
@@ -6245,10 +6242,10 @@
       <c r="AV56" s="2"/>
     </row>
     <row r="57" spans="2:48" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="183" t="s">
+      <c r="B57" s="180" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="184"/>
+      <c r="C57" s="181"/>
       <c r="D57" s="124"/>
       <c r="E57" s="37">
         <v>1483.9916422900001</v>
@@ -6256,10 +6253,10 @@
       <c r="F57" s="125">
         <v>1483.9916422900001</v>
       </c>
-      <c r="G57" s="190" t="s">
+      <c r="G57" s="187" t="s">
         <v>75</v>
       </c>
-      <c r="H57" s="184"/>
+      <c r="H57" s="181"/>
       <c r="I57" s="124">
         <v>772.89051418999998</v>
       </c>
@@ -6284,10 +6281,10 @@
       <c r="AV57" s="2"/>
     </row>
     <row r="58" spans="2:48" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="183" t="s">
+      <c r="B58" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="184"/>
+      <c r="C58" s="181"/>
       <c r="D58" s="124"/>
       <c r="E58" s="37">
         <v>1076.453</v>
@@ -6295,10 +6292,10 @@
       <c r="F58" s="125">
         <v>1076.453</v>
       </c>
-      <c r="G58" s="190" t="s">
+      <c r="G58" s="187" t="s">
         <v>77</v>
       </c>
-      <c r="H58" s="184"/>
+      <c r="H58" s="181"/>
       <c r="I58" s="124">
         <v>962.12684153999999</v>
       </c>
@@ -6323,10 +6320,10 @@
       <c r="AV58" s="2"/>
     </row>
     <row r="59" spans="2:48" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="187" t="s">
+      <c r="B59" s="184" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="188"/>
+      <c r="C59" s="185"/>
       <c r="D59" s="137">
         <v>3862.91740893</v>
       </c>
@@ -6336,10 +6333,10 @@
       <c r="F59" s="139">
         <v>857.42164242999979</v>
       </c>
-      <c r="G59" s="192" t="s">
+      <c r="G59" s="189" t="s">
         <v>79</v>
       </c>
-      <c r="H59" s="188"/>
+      <c r="H59" s="185"/>
       <c r="I59" s="137">
         <v>3406.4987710099999</v>
       </c>
@@ -6494,7 +6491,7 @@
       <c r="AV63" s="2"/>
     </row>
     <row r="64" spans="2:48" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B64" s="181" t="s">
+      <c r="B64" s="178" t="s">
         <v>82</v>
       </c>
       <c r="C64" s="111">
@@ -6506,7 +6503,7 @@
       <c r="E64" s="153">
         <v>-579.03563324999777</v>
       </c>
-      <c r="F64" s="189" t="s">
+      <c r="F64" s="186" t="s">
         <v>120</v>
       </c>
       <c r="G64" s="111">
@@ -6518,7 +6515,7 @@
       <c r="I64" s="153">
         <v>805.29117575000055</v>
       </c>
-      <c r="J64" s="189" t="s">
+      <c r="J64" s="186" t="s">
         <v>83</v>
       </c>
       <c r="K64" s="111">
@@ -6540,7 +6537,7 @@
       <c r="AV64" s="2"/>
     </row>
     <row r="65" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B65" s="183" t="s">
+      <c r="B65" s="180" t="s">
         <v>84</v>
       </c>
       <c r="C65" s="116">
@@ -6552,7 +6549,7 @@
       <c r="E65" s="125">
         <v>2146.952111430001</v>
       </c>
-      <c r="F65" s="190" t="s">
+      <c r="F65" s="187" t="s">
         <v>121</v>
       </c>
       <c r="G65" s="116">
@@ -6564,7 +6561,7 @@
       <c r="I65" s="125">
         <v>630.37215376000131</v>
       </c>
-      <c r="J65" s="190" t="s">
+      <c r="J65" s="187" t="s">
         <v>85</v>
       </c>
       <c r="K65" s="116">
@@ -6586,7 +6583,7 @@
       <c r="AV65" s="2"/>
     </row>
     <row r="66" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B66" s="183" t="s">
+      <c r="B66" s="180" t="s">
         <v>86</v>
       </c>
       <c r="C66" s="116">
@@ -6598,7 +6595,7 @@
       <c r="E66" s="125">
         <v>1619.2441838700011</v>
       </c>
-      <c r="F66" s="190" t="s">
+      <c r="F66" s="187" t="s">
         <v>122</v>
       </c>
       <c r="G66" s="116">
@@ -6610,7 +6607,7 @@
       <c r="I66" s="125">
         <v>-187.08377162000031</v>
       </c>
-      <c r="J66" s="190" t="s">
+      <c r="J66" s="187" t="s">
         <v>87</v>
       </c>
       <c r="K66" s="116">
@@ -6632,7 +6629,7 @@
       <c r="AV66" s="2"/>
     </row>
     <row r="67" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B67" s="183" t="s">
+      <c r="B67" s="180" t="s">
         <v>88</v>
       </c>
       <c r="C67" s="116">
@@ -6644,7 +6641,7 @@
       <c r="E67" s="125">
         <v>5769.212982750003</v>
       </c>
-      <c r="F67" s="190" t="s">
+      <c r="F67" s="187" t="s">
         <v>123</v>
       </c>
       <c r="G67" s="116">
@@ -6656,7 +6653,7 @@
       <c r="I67" s="117">
         <v>165.6236848900007</v>
       </c>
-      <c r="J67" s="190" t="s">
+      <c r="J67" s="187" t="s">
         <v>89</v>
       </c>
       <c r="K67" s="116">
@@ -6678,7 +6675,7 @@
       <c r="AV67" s="2"/>
     </row>
     <row r="68" spans="1:49" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B68" s="183" t="s">
+      <c r="B68" s="180" t="s">
         <v>90</v>
       </c>
       <c r="C68" s="116">
@@ -6690,7 +6687,7 @@
       <c r="E68" s="125">
         <v>-2088.9750640799998</v>
       </c>
-      <c r="F68" s="190" t="s">
+      <c r="F68" s="187" t="s">
         <v>124</v>
       </c>
       <c r="G68" s="116">
@@ -6702,7 +6699,7 @@
       <c r="I68" s="125">
         <v>468.5670458300001</v>
       </c>
-      <c r="J68" s="190" t="s">
+      <c r="J68" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K68" s="116">
@@ -6725,7 +6722,7 @@
     </row>
     <row r="69" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
-      <c r="B69" s="183" t="s">
+      <c r="B69" s="180" t="s">
         <v>92</v>
       </c>
       <c r="C69" s="116">
@@ -6737,7 +6734,7 @@
       <c r="E69" s="125">
         <v>-1609.55392947</v>
       </c>
-      <c r="F69" s="190" t="s">
+      <c r="F69" s="187" t="s">
         <v>125</v>
       </c>
       <c r="G69" s="116">
@@ -6749,7 +6746,7 @@
       <c r="I69" s="125">
         <v>-764.16536584000005</v>
       </c>
-      <c r="J69" s="190" t="s">
+      <c r="J69" s="187" t="s">
         <v>93</v>
       </c>
       <c r="K69" s="116">
@@ -6775,7 +6772,7 @@
     </row>
     <row r="70" spans="1:49" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
-      <c r="B70" s="183" t="s">
+      <c r="B70" s="180" t="s">
         <v>94</v>
       </c>
       <c r="C70" s="116">
@@ -6787,7 +6784,7 @@
       <c r="E70" s="125">
         <v>1782.6874409500001</v>
       </c>
-      <c r="F70" s="190" t="s">
+      <c r="F70" s="187" t="s">
         <v>126</v>
       </c>
       <c r="G70" s="116">
@@ -6799,7 +6796,7 @@
       <c r="I70" s="125">
         <v>495.91765198000002</v>
       </c>
-      <c r="J70" s="191" t="s">
+      <c r="J70" s="188" t="s">
         <v>95</v>
       </c>
       <c r="K70" s="119">
@@ -6825,7 +6822,7 @@
     </row>
     <row r="71" spans="1:49" s="7" customFormat="1" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
-      <c r="B71" s="183" t="s">
+      <c r="B71" s="180" t="s">
         <v>96</v>
       </c>
       <c r="C71" s="116">
@@ -6837,7 +6834,7 @@
       <c r="E71" s="125">
         <v>0</v>
       </c>
-      <c r="F71" s="190" t="s">
+      <c r="F71" s="187" t="s">
         <v>127</v>
       </c>
       <c r="G71" s="116">
@@ -6849,7 +6846,7 @@
       <c r="I71" s="125">
         <v>-7.5779734900000051</v>
       </c>
-      <c r="J71" s="190" t="s">
+      <c r="J71" s="187" t="s">
         <v>97</v>
       </c>
       <c r="K71" s="116">
@@ -6875,7 +6872,7 @@
     </row>
     <row r="72" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
-      <c r="B72" s="183" t="s">
+      <c r="B72" s="180" t="s">
         <v>98</v>
       </c>
       <c r="C72" s="116">
@@ -6887,7 +6884,7 @@
       <c r="E72" s="125">
         <v>2165.182011209999</v>
       </c>
-      <c r="F72" s="190" t="s">
+      <c r="F72" s="187" t="s">
         <v>128</v>
       </c>
       <c r="G72" s="116">
@@ -6899,7 +6896,7 @@
       <c r="I72" s="125">
         <v>0.1484156399999996</v>
       </c>
-      <c r="J72" s="190" t="s">
+      <c r="J72" s="187" t="s">
         <v>99</v>
       </c>
       <c r="K72" s="116">
@@ -6929,7 +6926,7 @@
     </row>
     <row r="73" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
-      <c r="B73" s="183" t="s">
+      <c r="B73" s="180" t="s">
         <v>100</v>
       </c>
       <c r="C73" s="116">
@@ -6941,7 +6938,7 @@
       <c r="E73" s="125">
         <v>601.99303155999996</v>
       </c>
-      <c r="F73" s="190" t="s">
+      <c r="F73" s="187" t="s">
         <v>129</v>
       </c>
       <c r="G73" s="116">
@@ -6953,7 +6950,7 @@
       <c r="I73" s="125">
         <v>1999.3345063100001</v>
       </c>
-      <c r="J73" s="190" t="s">
+      <c r="J73" s="187" t="s">
         <v>101</v>
       </c>
       <c r="K73" s="116">
@@ -6979,7 +6976,7 @@
     </row>
     <row r="74" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
-      <c r="B74" s="183" t="s">
+      <c r="B74" s="180" t="s">
         <v>102</v>
       </c>
       <c r="C74" s="116">
@@ -6991,7 +6988,7 @@
       <c r="E74" s="125">
         <v>-1069.10638279</v>
       </c>
-      <c r="F74" s="190" t="s">
+      <c r="F74" s="187" t="s">
         <v>130</v>
       </c>
       <c r="G74" s="116">
@@ -7003,7 +7000,7 @@
       <c r="I74" s="125">
         <v>-5.9906525399999992</v>
       </c>
-      <c r="J74" s="190" t="s">
+      <c r="J74" s="187" t="s">
         <v>103</v>
       </c>
       <c r="K74" s="116">
@@ -7029,7 +7026,7 @@
     </row>
     <row r="75" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
-      <c r="B75" s="183" t="s">
+      <c r="B75" s="180" t="s">
         <v>104</v>
       </c>
       <c r="C75" s="116">
@@ -7041,7 +7038,7 @@
       <c r="E75" s="125">
         <v>110.9370254999999</v>
       </c>
-      <c r="F75" s="190" t="s">
+      <c r="F75" s="187" t="s">
         <v>131</v>
       </c>
       <c r="G75" s="116">
@@ -7053,7 +7050,7 @@
       <c r="I75" s="125">
         <v>-128.48331564999989</v>
       </c>
-      <c r="J75" s="190" t="s">
+      <c r="J75" s="187" t="s">
         <v>105</v>
       </c>
       <c r="K75" s="116">
@@ -7079,7 +7076,7 @@
     </row>
     <row r="76" spans="1:49" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
-      <c r="B76" s="183" t="s">
+      <c r="B76" s="180" t="s">
         <v>106</v>
       </c>
       <c r="C76" s="116">
@@ -7091,7 +7088,7 @@
       <c r="E76" s="125">
         <v>0</v>
       </c>
-      <c r="F76" s="191" t="s">
+      <c r="F76" s="188" t="s">
         <v>132</v>
       </c>
       <c r="G76" s="119">
@@ -7103,7 +7100,7 @@
       <c r="I76" s="131">
         <v>230.17731089</v>
       </c>
-      <c r="J76" s="190" t="s">
+      <c r="J76" s="187" t="s">
         <v>107</v>
       </c>
       <c r="K76" s="116">
@@ -7129,7 +7126,7 @@
     </row>
     <row r="77" spans="1:49" s="7" customFormat="1" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
-      <c r="B77" s="183" t="s">
+      <c r="B77" s="180" t="s">
         <v>108</v>
       </c>
       <c r="C77" s="116">
@@ -7141,7 +7138,7 @@
       <c r="E77" s="125">
         <v>-1155.9299257799989</v>
       </c>
-      <c r="F77" s="190" t="s">
+      <c r="F77" s="187" t="s">
         <v>133</v>
       </c>
       <c r="G77" s="116">
@@ -7153,7 +7150,7 @@
       <c r="I77" s="125">
         <v>397.45221082</v>
       </c>
-      <c r="J77" s="190" t="s">
+      <c r="J77" s="187" t="s">
         <v>109</v>
       </c>
       <c r="K77" s="116">
@@ -7179,7 +7176,7 @@
     </row>
     <row r="78" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
-      <c r="B78" s="183" t="s">
+      <c r="B78" s="180" t="s">
         <v>110</v>
       </c>
       <c r="C78" s="116">
@@ -7191,7 +7188,7 @@
       <c r="E78" s="125">
         <v>126.2230860799999</v>
       </c>
-      <c r="F78" s="190" t="s">
+      <c r="F78" s="187" t="s">
         <v>134</v>
       </c>
       <c r="G78" s="116">
@@ -7203,7 +7200,7 @@
       <c r="I78" s="125">
         <v>500</v>
       </c>
-      <c r="J78" s="190" t="s">
+      <c r="J78" s="187" t="s">
         <v>111</v>
       </c>
       <c r="K78" s="116">
@@ -7229,7 +7226,7 @@
     </row>
     <row r="79" spans="1:49" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
-      <c r="B79" s="190" t="s">
+      <c r="B79" s="187" t="s">
         <v>112</v>
       </c>
       <c r="C79" s="116">
@@ -7241,7 +7238,7 @@
       <c r="E79" s="96">
         <v>-40</v>
       </c>
-      <c r="F79" s="190" t="s">
+      <c r="F79" s="187" t="s">
         <v>135</v>
       </c>
       <c r="G79" s="116">
@@ -7253,7 +7250,7 @@
       <c r="I79" s="117">
         <v>0</v>
       </c>
-      <c r="J79" s="190" t="s">
+      <c r="J79" s="187" t="s">
         <v>113</v>
       </c>
       <c r="K79" s="116">
@@ -7279,7 +7276,7 @@
     </row>
     <row r="80" spans="1:49" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
-      <c r="B80" s="192" t="s">
+      <c r="B80" s="189" t="s">
         <v>114</v>
       </c>
       <c r="C80" s="155">
@@ -7291,7 +7288,7 @@
       <c r="E80" s="139">
         <v>170.80870046999999</v>
       </c>
-      <c r="F80" s="190" t="s">
+      <c r="F80" s="187" t="s">
         <v>136</v>
       </c>
       <c r="G80" s="116">
@@ -7303,7 +7300,7 @@
       <c r="I80" s="117">
         <v>-500</v>
       </c>
-      <c r="J80" s="190" t="s">
+      <c r="J80" s="187" t="s">
         <v>115</v>
       </c>
       <c r="K80" s="116">
@@ -7333,7 +7330,7 @@
       <c r="C81" s="35"/>
       <c r="D81" s="37"/>
       <c r="E81" s="45"/>
-      <c r="F81" s="190" t="s">
+      <c r="F81" s="187" t="s">
         <v>137</v>
       </c>
       <c r="G81" s="116">
@@ -7345,7 +7342,7 @@
       <c r="I81" s="117">
         <v>7.5536377299999913</v>
       </c>
-      <c r="J81" s="190" t="s">
+      <c r="J81" s="187" t="s">
         <v>116</v>
       </c>
       <c r="K81" s="116">
@@ -7371,7 +7368,7 @@
     </row>
     <row r="82" spans="1:51" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
-      <c r="F82" s="190" t="s">
+      <c r="F82" s="187" t="s">
         <v>138</v>
       </c>
       <c r="G82" s="116">
@@ -7383,7 +7380,7 @@
       <c r="I82" s="96">
         <v>0.57715492000000168</v>
       </c>
-      <c r="J82" s="192" t="s">
+      <c r="J82" s="189" t="s">
         <v>117</v>
       </c>
       <c r="K82" s="155">
@@ -7409,7 +7406,7 @@
     </row>
     <row r="83" spans="1:51" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
-      <c r="F83" s="190" t="s">
+      <c r="F83" s="187" t="s">
         <v>139</v>
       </c>
       <c r="G83" s="116">
@@ -7436,7 +7433,7 @@
     <row r="84" spans="1:51" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="158"/>
-      <c r="F84" s="192" t="s">
+      <c r="F84" s="189" t="s">
         <v>140</v>
       </c>
       <c r="G84" s="155"/>
@@ -7549,7 +7546,7 @@
       <c r="J88" s="4"/>
       <c r="K88" s="5"/>
       <c r="L88" s="4"/>
-      <c r="M88" s="6"/>
+      <c r="M88" s="208"/>
       <c r="N88" s="145"/>
       <c r="P88" s="145"/>
       <c r="R88" s="11"/>
@@ -7574,10 +7571,10 @@
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
       <c r="I89" s="2"/>
-      <c r="J89" s="164"/>
-      <c r="K89" s="165"/>
-      <c r="L89" s="164"/>
-      <c r="M89" s="166"/>
+      <c r="J89" s="208"/>
+      <c r="K89" s="209"/>
+      <c r="L89" s="208"/>
+      <c r="M89" s="208"/>
       <c r="N89" s="145"/>
       <c r="P89" s="145"/>
       <c r="R89" s="11"/>
@@ -7602,10 +7599,10 @@
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
+      <c r="J90" s="208"/>
+      <c r="K90" s="209"/>
+      <c r="L90" s="208"/>
+      <c r="M90" s="208"/>
       <c r="N90" s="145"/>
       <c r="P90" s="145"/>
       <c r="R90" s="11"/>
@@ -7971,7 +7968,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="145"/>
-      <c r="P103" s="167"/>
+      <c r="P103" s="164"/>
       <c r="R103" s="11"/>
       <c r="S103" s="11"/>
       <c r="AQ103" s="8"/>
@@ -8195,7 +8192,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
       <c r="N111" s="145"/>
-      <c r="P111" s="167"/>
+      <c r="P111" s="164"/>
       <c r="R111" s="11"/>
       <c r="S111" s="11"/>
       <c r="AQ111" s="8"/>
@@ -8223,7 +8220,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
       <c r="N112" s="145"/>
-      <c r="P112" s="167"/>
+      <c r="P112" s="164"/>
       <c r="R112" s="11"/>
       <c r="S112" s="11"/>
       <c r="AQ112" s="8"/>
@@ -15677,7 +15674,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="3.937007874015748E-2" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>
-  <pageSetup paperSize="9" scale="44" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="43" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
